--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.86.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.86.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.86.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.86.xlsx
@@ -423,17 +423,17 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.86.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.86.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0086.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0086.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -599,18 +599,18 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: sso.â€�</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: ï»¿â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L31: isolated marker/symbol line :: 79</t>
@@ -618,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L7: isolated marker/symbol line :: 79</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -667,11 +667,7 @@
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: so.â€�</t>
-        </is>
-      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -681,7 +677,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 4</t>
+          <t>L7: isolated marker/symbol line :: 79</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -730,7 +726,11 @@
           <t>L83: isolated marker/symbol line :: `</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L79: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
